--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4723,7 +4999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1079969-10-CM25</t>
+          <t>1079969-11-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4771,14 +5047,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>409.91</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5028,7 +5324,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1079969-11-CM25</t>
+          <t>4928-12-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5053,7 +5349,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5076,20 +5372,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>948.4400000000001</v>
+        <v>42015.55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4928-12-CM25</t>
+          <t>1079969-10-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5114,7 +5414,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5137,14 +5437,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>42015.55</v>
+        <v>409.91</v>
       </c>
     </row>
     <row r="78">
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6431,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2561-35-CM25</t>
+          <t>957865-60-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.004.035-7</t>
+          <t>61.980.820-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6479,20 +6867,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5203.94</v>
+        <v>3795.76</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>957865-60-CM25</t>
+          <t>2561-35-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>61.004.035-7</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6540,14 +6932,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3795.76</v>
+        <v>5203.94</v>
       </c>
     </row>
     <row r="101">
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7102,7 +7534,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079969-15-CM25</t>
+          <t>1386073-24-SE25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7559,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>71.004.200-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP CULTURAL DE LAS CONDES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7150,20 +7582,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>528.98</v>
+        <v>116672.39</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2137-125-CM25</t>
+          <t>1079969-15-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7614,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,17 +7624,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7211,20 +7647,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12900.95</v>
+        <v>528.98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2554-1-CM25</t>
+          <t>2137-125-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,17 +7689,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7272,20 +7712,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2619.84</v>
+        <v>12900.95</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1665-110-CM25</t>
+          <t>2554-1-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,22 +7749,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7333,20 +7777,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9410.219999999999</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1075956-9-CM25</t>
+          <t>1665-110-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,22 +7814,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7394,20 +7842,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>387.65</v>
+        <v>9410.219999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1514-6777-CM25</t>
+          <t>1075956-9-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,17 +7884,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.602.275-k</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7455,20 +7907,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>41244.29</v>
+        <v>387.65</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3951-54-CM25</t>
+          <t>1514-6777-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,17 +7949,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.275-k</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7516,20 +7972,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7672.72</v>
+        <v>41244.29</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2744-25-CM25</t>
+          <t>3951-54-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,22 +8009,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7577,20 +8037,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6237.72</v>
+        <v>7672.72</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>778998-8-CM25</t>
+          <t>2744-25-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,22 +8074,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7638,20 +8102,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2174.29</v>
+        <v>6237.72</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3481-17-CM25</t>
+          <t>778998-8-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,7 +8144,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7686,7 +8154,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7699,20 +8167,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1039.54</v>
+        <v>2174.29</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3481-18-CM25</t>
+          <t>3481-17-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7760,20 +8232,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3118.86</v>
+        <v>1039.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1075956-10-CM25</t>
+          <t>3481-18-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +8264,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,17 +8274,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7821,20 +8297,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>201.1</v>
+        <v>3118.86</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2554-2-CM25</t>
+          <t>1075956-10-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,17 +8339,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7882,20 +8362,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>752.64</v>
+        <v>201.1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>619133-953-CM25</t>
+          <t>2554-2-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,17 +8404,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7943,20 +8427,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>26273.74</v>
+        <v>752.64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3522-12-CM25</t>
+          <t>619133-953-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,17 +8469,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.101.055-9</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8004,20 +8492,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>209.07</v>
+        <v>26273.74</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4062-134-CM25</t>
+          <t>3522-12-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8042,17 +8534,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.101.055-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8065,20 +8557,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>731.74</v>
+        <v>209.07</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1075956-11-CM25</t>
+          <t>4062-134-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,17 +8599,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8126,20 +8622,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>322.75</v>
+        <v>731.74</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4100-7-CM25</t>
+          <t>1075956-11-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8187,20 +8687,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7030.93</v>
+        <v>322.75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057384-133-CM25</t>
+          <t>4100-7-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,17 +8729,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8248,20 +8752,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2432.6</v>
+        <v>7030.93</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>761-73-CM25</t>
+          <t>1057384-133-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8286,17 +8794,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8309,20 +8817,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6217.21</v>
+        <v>2432.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3387-18-CM25</t>
+          <t>761-73-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8859,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.101.008-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8370,20 +8882,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1243.95</v>
+        <v>6217.21</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>952946-24-CM25</t>
+          <t>3387-18-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,7 +8924,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.101.008-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8418,7 +8934,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8431,20 +8947,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1045.34</v>
+        <v>1243.95</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>643553-84-CM25</t>
+          <t>952946-24-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,22 +8984,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>71.455.500-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE SN JOAQUIN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8492,20 +9012,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>7090.52</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3374-23-CM25</t>
+          <t>643553-84-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8525,22 +9049,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>71.455.500-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE SN JOAQUIN</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8553,20 +9077,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2613.34</v>
+        <v>7090.52</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>761-74-CM25</t>
+          <t>3374-23-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,17 +9119,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8614,20 +9142,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1287.67</v>
+        <v>2613.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3530-9-CM25</t>
+          <t>761-74-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8652,17 +9184,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.943.600-8</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8675,20 +9207,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1045.34</v>
+        <v>1287.67</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3950-951-CM25</t>
+          <t>3530-9-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,27 +9239,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.943.600-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8736,20 +9272,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4282.16</v>
+        <v>1045.34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1075956-13-CM25</t>
+          <t>3950-951-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8769,22 +9309,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8797,20 +9337,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>555.28</v>
+        <v>4282.16</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>734-99-CM25</t>
+          <t>1075956-13-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,17 +9379,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8858,20 +9402,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>30960.64</v>
+        <v>555.28</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2139-2523-CM25</t>
+          <t>734-99-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8896,17 +9444,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.312-8</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8919,20 +9467,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7299.69</v>
+        <v>30960.64</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1692-88-CM25</t>
+          <t>2139-2523-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,17 +9509,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.312-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8980,20 +9532,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>11854.24</v>
+        <v>7299.69</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1079967-34-CM25</t>
+          <t>1692-88-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,17 +9574,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9041,20 +9597,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3739.39</v>
+        <v>11854.24</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3950-949-CM25</t>
+          <t>1079967-34-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,22 +9634,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9102,20 +9662,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>9304.700000000001</v>
+        <v>3739.39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4343-68-CM25</t>
+          <t>3950-949-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,22 +9699,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9163,20 +9727,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>23175.71</v>
+        <v>9304.700000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3316-32-CM25</t>
+          <t>4343-68-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,17 +9769,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9224,20 +9792,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3234.13</v>
+        <v>23175.71</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4452-181-CM25</t>
+          <t>3316-32-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,22 +9829,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9285,20 +9857,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>19152.81</v>
+        <v>3234.13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1142-48-CM25</t>
+          <t>4452-181-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,22 +9889,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9346,20 +9922,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5057.79</v>
+        <v>19152.81</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4051-53-CM25</t>
+          <t>1142-48-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,22 +9959,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9407,20 +9987,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>17604.32</v>
+        <v>5057.79</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1288512-8-CM25</t>
+          <t>4051-53-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9440,22 +10024,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9468,20 +10052,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1822.85</v>
+        <v>17604.32</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3765-84-CM25</t>
+          <t>1288512-8-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,17 +10094,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9529,20 +10117,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8210.4</v>
+        <v>1822.85</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1681-119-CM25</t>
+          <t>3765-84-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,17 +10159,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9590,20 +10182,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>205.26</v>
+        <v>8210.4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1005498-30-CM25</t>
+          <t>1681-119-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,17 +10224,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9651,20 +10247,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>53230.47</v>
+        <v>205.26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3949-70-CM25</t>
+          <t>1005498-30-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +10279,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,17 +10289,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9712,20 +10312,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>11583.79</v>
+        <v>53230.47</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3399-14-CM25</t>
+          <t>3949-70-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9750,17 +10354,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9773,20 +10377,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>531.15</v>
+        <v>11583.79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>377-83-CM25</t>
+          <t>3399-14-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9811,17 +10419,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9834,20 +10442,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>14224.93</v>
+        <v>531.15</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057476-176-CM25</t>
+          <t>377-83-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,17 +10484,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.608.003-2</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9895,20 +10507,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2552.67</v>
+        <v>14224.93</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1057476-177-CM25</t>
+          <t>1057476-176-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9956,20 +10572,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>265.9</v>
+        <v>2552.67</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>651-38-CM25</t>
+          <t>1057476-177-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,22 +10609,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.608.003-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10017,20 +10637,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>464.56</v>
+        <v>265.9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1057514-74-CM25</t>
+          <t>651-38-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10050,22 +10674,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10078,20 +10702,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13676.82</v>
+        <v>464.56</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3617-27-CM25</t>
+          <t>1057514-74-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,17 +10744,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10139,20 +10767,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5279.11</v>
+        <v>13676.82</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>721703-37-CM25</t>
+          <t>3617-27-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,17 +10809,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10200,20 +10832,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3800.96</v>
+        <v>5279.11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1057476-175-CM25</t>
+          <t>721703-37-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10238,12 +10874,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.608.003-2</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10261,20 +10897,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>846.0599999999999</v>
+        <v>3800.96</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2151-46-CM25</t>
+          <t>1057476-175-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10929,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,17 +10939,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.608.003-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10322,20 +10962,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7126.77</v>
+        <v>846.0599999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1335445-5-CM25</t>
+          <t>2151-46-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10360,17 +11004,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10383,20 +11027,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1267.89</v>
+        <v>7126.77</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3361-14-CM25</t>
+          <t>1335445-5-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10421,17 +11069,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10444,20 +11092,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>527.21</v>
+        <v>1267.89</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1057420-128-CM25</t>
+          <t>3361-14-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10482,17 +11134,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10505,20 +11157,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>19175.32</v>
+        <v>527.21</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1643-625-CM25</t>
+          <t>1057420-128-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10543,17 +11199,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10566,20 +11222,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>11166.95</v>
+        <v>19175.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5240-25-CM25</t>
+          <t>1643-625-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10604,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10627,20 +11287,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1869.15</v>
+        <v>11166.95</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3970-3-CM25</t>
+          <t>5240-25-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10665,7 +11329,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10688,20 +11352,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>33384.39</v>
+        <v>1869.15</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1260057-7595-CM25</t>
+          <t>3970-3-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +11394,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.602.121-4</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10749,20 +11417,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4524.27</v>
+        <v>33384.39</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>881-30-CM25</t>
+          <t>1260057-7595-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,17 +11459,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.602.121-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10810,20 +11482,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2888.8</v>
+        <v>4524.27</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2046-80-CM25</t>
+          <t>881-30-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,17 +11524,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10871,20 +11547,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>16824.38</v>
+        <v>2888.8</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>620279-29-CM25</t>
+          <t>2046-80-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10909,17 +11589,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10932,20 +11612,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>34494.39</v>
+        <v>16824.38</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>707409-20-CM25</t>
+          <t>620279-29-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,17 +11654,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10993,20 +11677,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1786.41</v>
+        <v>34494.39</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3532-9-CM25</t>
+          <t>707409-20-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11031,17 +11719,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11054,20 +11742,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>965.88</v>
+        <v>1786.41</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>707419-14-CM25</t>
+          <t>3532-9-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,27 +11774,27 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11115,20 +11807,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>70621.19</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1552-4645-CM25</t>
+          <t>707419-14-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11148,22 +11844,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11176,20 +11872,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>23114.59</v>
+        <v>70621.19</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>813685-26-CM25</t>
+          <t>1552-4645-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11214,17 +11914,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11237,20 +11937,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>19629.78</v>
+        <v>23114.59</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057388-77-CM25</t>
+          <t>813685-26-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11270,22 +11974,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11298,20 +12002,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>11871.56</v>
+        <v>19629.78</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5360-71-CM25</t>
+          <t>1057388-77-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11336,17 +12044,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11359,20 +12067,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>9514.84</v>
+        <v>11871.56</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>617807-1529-CM25</t>
+          <t>5360-71-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,17 +12109,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11420,20 +12132,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>15517.23</v>
+        <v>9514.84</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1075956-17-CM25</t>
+          <t>617807-1529-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11448,27 +12164,27 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11481,20 +12197,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>198.62</v>
+        <v>15517.23</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3617-39-CM25</t>
+          <t>1075956-17-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11519,17 +12239,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11542,20 +12262,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2646.49</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3827-83-CM25</t>
+          <t>3617-39-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11580,17 +12304,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11603,20 +12327,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>25405.95</v>
+        <v>2646.49</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1383-69-CM25</t>
+          <t>3827-83-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11636,22 +12364,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11664,20 +12392,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>8606.969999999999</v>
+        <v>25405.95</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1075956-19-CM25</t>
+          <t>1383-69-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11697,22 +12429,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11725,20 +12457,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>626.03</v>
+        <v>8606.969999999999</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1075956-18-CM25</t>
+          <t>1075956-19-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11786,20 +12522,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>37.71</v>
+        <v>626.03</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1038-24-CM25</t>
+          <t>1075956-18-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,17 +12564,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11847,20 +12587,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6481.77</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1099899-39-CM25</t>
+          <t>1038-24-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11885,17 +12629,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11908,20 +12652,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6615.25</v>
+        <v>6481.77</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1038-23-CM25</t>
+          <t>1099899-39-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,17 +12694,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11969,20 +12717,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5833.91</v>
+        <v>6615.25</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>769-4213-CM25</t>
+          <t>1038-23-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,17 +12759,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12030,20 +12782,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>70925.74000000001</v>
+        <v>5833.91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1557-76-CM25</t>
+          <t>769-4213-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,17 +12824,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12091,20 +12847,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18101.94</v>
+        <v>70925.74000000001</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3474-157-CM25</t>
+          <t>1557-76-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12129,17 +12889,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12152,20 +12912,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>14642.96</v>
+        <v>18101.94</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4434-7-CM25</t>
+          <t>3474-157-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12190,17 +12954,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12213,20 +12977,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1032.87</v>
+        <v>14642.96</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3365-21-CM25</t>
+          <t>4434-7-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12251,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12274,20 +13042,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2115.07</v>
+        <v>1032.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2138-46-CM25</t>
+          <t>3365-21-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12312,17 +13084,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12335,20 +13107,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>11644.52</v>
+        <v>2115.07</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1968-323-CM25</t>
+          <t>2138-46-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,17 +13149,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12396,20 +13172,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>38109.35</v>
+        <v>11644.52</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1070329-62-CM25</t>
+          <t>1968-323-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12434,17 +13214,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12457,20 +13237,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>13571.03</v>
+        <v>38109.35</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1079694-22-CM25</t>
+          <t>1070329-62-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,7 +13269,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12495,17 +13279,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12518,20 +13302,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>20625.15</v>
+        <v>13571.03</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3412-26-CM25</t>
+          <t>1079694-22-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,7 +13334,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12556,17 +13344,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12579,20 +13367,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1060.99</v>
+        <v>20625.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4848-72-CM25</t>
+          <t>3412-26-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12612,22 +13404,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12640,20 +13432,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>16925.73</v>
+        <v>1060.99</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1371-8-CM25</t>
+          <t>4848-72-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,22 +13469,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12701,20 +13497,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>699.8099999999999</v>
+        <v>16925.73</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1075956-22-CM25</t>
+          <t>1371-8-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12739,12 +13539,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12762,20 +13562,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>100.79</v>
+        <v>699.8099999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>853-62-CM25</t>
+          <t>1075956-22-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,17 +13604,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12823,20 +13627,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1272.78</v>
+        <v>100.79</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>853-61-CM25</t>
+          <t>853-62-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12884,20 +13692,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2415.58</v>
+        <v>1272.78</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>853-60-CM25</t>
+          <t>853-61-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12945,20 +13757,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1272.78</v>
+        <v>2415.58</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1075956-21-CM25</t>
+          <t>853-60-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12983,17 +13799,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13006,20 +13822,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>322.54</v>
+        <v>1272.78</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>853-56-CM25</t>
+          <t>1075956-21-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13044,17 +13864,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13067,20 +13887,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>16744.39</v>
+        <v>322.54</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>853-55-CM25</t>
+          <t>853-56-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13128,20 +13952,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>36279.51</v>
+        <v>16744.39</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>945256-19-CM25</t>
+          <t>853-55-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,17 +13994,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.980.790-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13189,20 +14017,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2121.94</v>
+        <v>36279.51</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2085-148-CM25</t>
+          <t>945256-19-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,17 +14059,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.980.790-1</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13250,20 +14082,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>25012.94</v>
+        <v>2121.94</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3412-28-CM25</t>
+          <t>2085-148-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13283,22 +14119,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13311,20 +14147,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1589.36</v>
+        <v>25012.94</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>853-58-CM25</t>
+          <t>3412-28-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,22 +14184,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13372,20 +14212,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2415.58</v>
+        <v>1589.36</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1075956-25-CM25</t>
+          <t>853-58-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13400,7 +14244,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13410,17 +14254,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13433,20 +14277,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>509.13</v>
+        <v>2415.58</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1057496-416-CM25</t>
+          <t>1075956-25-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13471,12 +14319,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.608.105-5</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13494,20 +14342,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>8448.09</v>
+        <v>509.13</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1057512-291-CM25</t>
+          <t>1057496-416-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,17 +14384,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>61.608.105-5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13555,20 +14407,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>12111.31</v>
+        <v>8448.09</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2045-59-CM25</t>
+          <t>1057512-291-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13593,17 +14449,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13616,20 +14472,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8448.09</v>
+        <v>12111.31</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3474-143-CM25</t>
+          <t>2045-59-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13654,17 +14514,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13677,20 +14537,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>23709.87</v>
+        <v>8448.09</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1353712-9-CM25</t>
+          <t>3474-143-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13715,17 +14579,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.981.150-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13738,20 +14602,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1740.58</v>
+        <v>23709.87</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1079639-85-CM25</t>
+          <t>1353712-9-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,17 +14644,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.981.150-K</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13799,20 +14667,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>53183.69</v>
+        <v>1740.58</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3951-57-CM25</t>
+          <t>1079639-85-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,17 +14709,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13860,20 +14732,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>8472.110000000001</v>
+        <v>53183.69</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1075956-28-CM25</t>
+          <t>3951-57-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13888,7 +14764,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,17 +14774,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13921,20 +14797,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>389.19</v>
+        <v>8472.110000000001</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057536-1488-CM25</t>
+          <t>1075956-28-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13959,17 +14839,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -13982,20 +14862,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2926.02</v>
+        <v>389.19</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1057536-1485-CM25</t>
+          <t>1057536-1488-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14043,20 +14927,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2001.21</v>
+        <v>2926.02</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1402-102-CM25</t>
+          <t>1057536-1485-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14081,17 +14969,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14104,20 +14992,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1062.71</v>
+        <v>2001.21</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>585-28-CM25</t>
+          <t>1402-102-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14137,22 +15029,22 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14165,20 +15057,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>347.7</v>
+        <v>1062.71</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>585-27-CM25</t>
+          <t>585-28-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14226,20 +15122,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>25998.68</v>
+        <v>347.7</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1075956-27-CM25</t>
+          <t>585-27-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14259,17 +15159,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14287,20 +15187,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>196.87</v>
+        <v>25998.68</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1057506-265-CM25</t>
+          <t>1075956-27-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14325,17 +15229,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14348,20 +15252,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>16296.67</v>
+        <v>196.87</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1464-287-CM25</t>
+          <t>1057506-265-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14386,17 +15294,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14409,20 +15317,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>22225.79</v>
+        <v>16296.67</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5194-26-CM25</t>
+          <t>1464-287-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14447,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.004.108-6</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14470,20 +15382,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>212.54</v>
+        <v>22225.79</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>654478-54-CM25</t>
+          <t>5194-26-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14508,12 +15424,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.004.108-6</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14531,20 +15447,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3506.94</v>
+        <v>212.54</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4968-2992-CM25</t>
+          <t>654478-54-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14569,17 +15489,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14592,20 +15512,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>3724.32</v>
+        <v>3506.94</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1039-79-CM25</t>
+          <t>4968-2992-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14630,17 +15554,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14653,20 +15577,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1284.99</v>
+        <v>3724.32</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1973-1730-CM25</t>
+          <t>1039-79-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14691,12 +15619,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14714,20 +15642,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>744.3099999999999</v>
+        <v>1284.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1039-75-CM25</t>
+          <t>1973-1730-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14752,12 +15684,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14775,20 +15707,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4154.64</v>
+        <v>744.3099999999999</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1075956-26-CM25</t>
+          <t>1039-75-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14813,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14836,20 +15772,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4911.58</v>
+        <v>4154.64</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1057534-232-CM25</t>
+          <t>1075956-26-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14864,7 +15804,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14874,17 +15814,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14897,20 +15837,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>21236.83</v>
+        <v>4911.58</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>707427-14-CM25</t>
+          <t>1057534-232-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14930,22 +15874,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -14958,20 +15902,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2439.16</v>
+        <v>21236.83</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1057540-6794-CM25</t>
+          <t>707427-14-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14991,22 +15939,22 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15019,20 +15967,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>75656.22</v>
+        <v>2439.16</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1529-66-CM25</t>
+          <t>1057540-6794-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15057,17 +16009,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15080,20 +16032,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>43909.96</v>
+        <v>75656.22</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5911-44-CM25</t>
+          <t>1529-66-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,17 +16074,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15141,20 +16097,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>10325.56</v>
+        <v>43909.96</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1057385-73-CM25</t>
+          <t>5911-44-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15179,17 +16139,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15202,20 +16162,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2017.5</v>
+        <v>10325.56</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1965-107-CM25</t>
+          <t>1057385-73-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15240,17 +16204,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15263,20 +16227,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8402.879999999999</v>
+        <v>2017.5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1099899-43-CM25</t>
+          <t>1965-107-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15301,17 +16269,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15324,20 +16292,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1281.11</v>
+        <v>8402.879999999999</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>652-64-CM25</t>
+          <t>1099899-43-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15362,17 +16334,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15385,20 +16357,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>31866</v>
+        <v>1281.11</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1681-146-CM25</t>
+          <t>652-64-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15423,17 +16399,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15446,20 +16422,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>28645.46</v>
+        <v>31866</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1681-145-CM25</t>
+          <t>1681-146-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15479,7 +16459,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15507,20 +16487,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>41419.26</v>
+        <v>28645.46</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>418-673-CM25</t>
+          <t>1681-145-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15540,22 +16524,22 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15568,20 +16552,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>28430.81</v>
+        <v>41419.26</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>875646-502-CM25</t>
+          <t>418-673-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15606,17 +16594,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.602.057-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15629,20 +16617,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>31775.61</v>
+        <v>28430.81</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1057506-271-CM25</t>
+          <t>875646-502-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15667,17 +16659,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.602.057-9</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15690,20 +16682,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5925.08</v>
+        <v>31775.61</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2186-185-CM25</t>
+          <t>1057506-271-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15718,7 +16714,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15728,17 +16724,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15751,20 +16747,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>8319.4</v>
+        <v>5925.08</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>707427-15-CM25</t>
+          <t>2186-185-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15784,22 +16784,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15812,20 +16812,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1784.95</v>
+        <v>8319.4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1620-64-CM25</t>
+          <t>707427-15-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15845,22 +16849,22 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15873,20 +16877,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>17827.29</v>
+        <v>1784.95</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3450-6-CM25</t>
+          <t>1620-64-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15911,17 +16919,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.101.026-5</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15934,20 +16942,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1574.74</v>
+        <v>17827.29</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5349-459-CM25</t>
+          <t>3450-6-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15972,17 +16984,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.101.026-5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -15995,20 +17007,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>49468.46</v>
+        <v>1574.74</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>812261-2651-CM25</t>
+          <t>5349-459-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16033,17 +17049,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16056,20 +17072,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1674.67</v>
+        <v>49468.46</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1077908-44-CM25</t>
+          <t>812261-2651-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16094,17 +17114,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16117,20 +17137,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>32767.23</v>
+        <v>1674.67</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>813685-28-CM25</t>
+          <t>1077908-44-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16155,17 +17179,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16178,20 +17202,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>7130.92</v>
+        <v>32767.23</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1978-211-CM25</t>
+          <t>813685-28-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16211,22 +17239,22 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16239,20 +17267,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>21917.08</v>
+        <v>7130.92</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2102-193-CM25</t>
+          <t>1978-211-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16272,22 +17304,22 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16300,20 +17332,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>27365.94</v>
+        <v>21917.08</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1079454-78-CM25</t>
+          <t>2102-193-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16333,22 +17369,22 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16361,20 +17397,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>32440.18</v>
+        <v>27365.94</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1288-77-CM25</t>
+          <t>1079454-78-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16394,22 +17434,22 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16422,20 +17462,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>41946.57</v>
+        <v>32440.18</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1590-116-CM25</t>
+          <t>1288-77-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16460,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16483,20 +17527,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4218.63</v>
+        <v>41946.57</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1590-115-CM25</t>
+          <t>1590-116-CM25</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16544,20 +17592,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1433.96</v>
+        <v>4218.63</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2021-9-CM25</t>
+          <t>1590-115-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16582,12 +17634,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16616,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>165788.84</v>
+        <v>1433.96</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>688-24-CM25</t>
+          <t>2021-9-CM25</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16647,12 +17699,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16670,74 +17722,147 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1793.3</v>
+        <v>165788.84</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>688-24-CM25</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>61.301.100-5</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>1793.3</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
           <t>2107-327-CM25</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>feb-2025</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
         <is>
           <t>61.602.148-6</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G268" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H268" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M267" s="2" t="n">
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
         <v>44154.29</v>
       </c>
     </row>
